--- a/Logs/Incoming Inspection Logs/MDL-004_Incoming_Inspection.xlsx
+++ b/Logs/Incoming Inspection Logs/MDL-004_Incoming_Inspection.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="66">
   <si>
     <t xml:space="preserve">Incoming Inspection Log</t>
   </si>
@@ -79,6 +79,147 @@
   </si>
   <si>
     <t xml:space="preserve">CC0603226010AABX5R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P00002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1206106050AAAX7R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC0603104050AAAX7R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC1210226025AAAX7R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC0805226025AABX5R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEA771MS107M1JLAS018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC0603103050AAAX7R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC0603474050AAAX7R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPTBP04R1-500-02BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPTBP04R1-500-03BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPTBP04R1-500-04BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KUSB4105-GF-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KHS4B-PH-SM4-TB(LF)(SN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLQ62702P5179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSSS26SHE3_B_H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVSCDSOT23-SM712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLLS R976-NR-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMAP63203WU-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMAP63205WU-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP32-WROOM-32UE-N16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCP2102C-A01-GQFN28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UDRV8825PWPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTMP36GRTZ-REEL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSRP2512-2R2M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QTCMT1600T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QBC847BDW1T1G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0603330075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0603510075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0603682075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC060310K2075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0805121150AAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC12101K2200AAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC060322K1075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC060347K5075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC06031K0075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC06031M0075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC08050R2075AAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC060350K075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC060330K075AAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW435151014845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP5010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPTBP04P1-500-02BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPTBP04P1-500-03BE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPPHR-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTSPH-002T-P0.5L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FANDC5V4040mmPWMTACH</t>
   </si>
 </sst>
 </file>
@@ -321,6 +462,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -472,740 +614,1752 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
+      <c r="A6" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="5"/>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J6" s="5"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
+      <c r="M6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="5"/>
+      <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J7" s="5"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="5"/>
+      <c r="A8" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="5"/>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J8" s="5"/>
-      <c r="K8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="5"/>
+      <c r="A9" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="5"/>
+      <c r="H9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
+      <c r="M9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="5"/>
+      <c r="A10" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="5"/>
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J10" s="5"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
+      <c r="M10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="5"/>
+      <c r="A11" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="5"/>
+      <c r="H11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J11" s="5"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
+      <c r="M11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="5"/>
+      <c r="A12" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="5"/>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J12" s="5"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="5"/>
+      <c r="A13" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="5"/>
+      <c r="H13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J13" s="5"/>
-      <c r="K13" s="3"/>
+      <c r="K13" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
+      <c r="M13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="5"/>
+      <c r="A14" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="5"/>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
+      <c r="M14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="5"/>
+      <c r="A15" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="5"/>
+      <c r="H15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J15" s="5"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
+      <c r="M15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="5"/>
+      <c r="A16" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="5"/>
+      <c r="H16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J16" s="5"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="M16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="5"/>
+      <c r="A17" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="G17" s="5"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="5"/>
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J17" s="5"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
+      <c r="M17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="5"/>
+      <c r="A18" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="5"/>
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J18" s="5"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
+      <c r="M18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="5"/>
+      <c r="A19" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>34</v>
+      </c>
       <c r="G19" s="5"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="5"/>
+      <c r="H19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J19" s="5"/>
-      <c r="K19" s="3"/>
+      <c r="K19" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
+      <c r="M19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="5"/>
+      <c r="A20" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="5"/>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J20" s="5"/>
-      <c r="K20" s="3"/>
+      <c r="K20" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
+      <c r="M20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="5"/>
+      <c r="A21" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="5"/>
+      <c r="H21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J21" s="5"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
+      <c r="M21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="5"/>
+      <c r="A22" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="5"/>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J22" s="5"/>
-      <c r="K22" s="3"/>
+      <c r="K22" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
+      <c r="M22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="5"/>
+      <c r="A23" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="G23" s="5"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="5"/>
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J23" s="5"/>
-      <c r="K23" s="3"/>
+      <c r="K23" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+      <c r="M23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="5"/>
+      <c r="A24" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="G24" s="5"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="5"/>
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J24" s="5"/>
-      <c r="K24" s="3"/>
+      <c r="K24" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
+      <c r="M24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="5"/>
+      <c r="A25" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="G25" s="5"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="5"/>
+      <c r="H25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J25" s="5"/>
-      <c r="K25" s="3"/>
+      <c r="K25" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+      <c r="M25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="5"/>
+      <c r="A26" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="G26" s="5"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="5"/>
+      <c r="H26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J26" s="5"/>
-      <c r="K26" s="3"/>
+      <c r="K26" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
+      <c r="M26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="5"/>
+      <c r="A27" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="G27" s="5"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="5"/>
+      <c r="H27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J27" s="5"/>
-      <c r="K27" s="3"/>
+      <c r="K27" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="M27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="5"/>
+      <c r="A28" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="G28" s="5"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="5"/>
+      <c r="H28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J28" s="5"/>
-      <c r="K28" s="3"/>
+      <c r="K28" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
+      <c r="M28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="5"/>
+      <c r="A29" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="G29" s="5"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="5"/>
+      <c r="H29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J29" s="5"/>
-      <c r="K29" s="3"/>
+      <c r="K29" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
+      <c r="M29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="5"/>
+      <c r="A30" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="G30" s="5"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="5"/>
+      <c r="H30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J30" s="5"/>
-      <c r="K30" s="3"/>
+      <c r="K30" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
+      <c r="M30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="5"/>
+      <c r="A31" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="G31" s="5"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="5"/>
+      <c r="H31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J31" s="5"/>
-      <c r="K31" s="3"/>
+      <c r="K31" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
+      <c r="M31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="5"/>
+      <c r="A32" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="G32" s="5"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="5"/>
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J32" s="5"/>
-      <c r="K32" s="3"/>
+      <c r="K32" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
+      <c r="M32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="5"/>
+      <c r="A33" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="G33" s="5"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="5"/>
+      <c r="H33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J33" s="5"/>
-      <c r="K33" s="3"/>
+      <c r="K33" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
+      <c r="M33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="5"/>
+      <c r="A34" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="G34" s="5"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="5"/>
+      <c r="H34" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J34" s="5"/>
-      <c r="K34" s="3"/>
+      <c r="K34" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
+      <c r="M34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="5"/>
+      <c r="A35" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="G35" s="5"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="5"/>
+      <c r="H35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J35" s="5"/>
-      <c r="K35" s="3"/>
+      <c r="K35" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
+      <c r="M35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="5"/>
+      <c r="A36" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="G36" s="5"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="5"/>
+      <c r="H36" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J36" s="5"/>
-      <c r="K36" s="3"/>
+      <c r="K36" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
+      <c r="M36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="5"/>
+      <c r="A37" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>52</v>
+      </c>
       <c r="G37" s="5"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="5"/>
+      <c r="H37" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J37" s="5"/>
-      <c r="K37" s="3"/>
+      <c r="K37" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L37" s="3"/>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
+      <c r="M37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="5"/>
+      <c r="A38" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="G38" s="5"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="5"/>
+      <c r="H38" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J38" s="5"/>
-      <c r="K38" s="3"/>
+      <c r="K38" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
+      <c r="M38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="5"/>
+      <c r="A39" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>54</v>
+      </c>
       <c r="G39" s="5"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="5"/>
+      <c r="H39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J39" s="5"/>
-      <c r="K39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
+      <c r="M39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="5"/>
+      <c r="A40" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="G40" s="5"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="5"/>
+      <c r="H40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J40" s="5"/>
-      <c r="K40" s="3"/>
+      <c r="K40" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
+      <c r="M40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="5"/>
+      <c r="A41" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>56</v>
+      </c>
       <c r="G41" s="5"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="5"/>
+      <c r="H41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J41" s="5"/>
-      <c r="K41" s="3"/>
+      <c r="K41" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
+      <c r="M41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="5"/>
+      <c r="A42" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G42" s="5"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="5"/>
+      <c r="H42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="3"/>
+      <c r="K42" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
+      <c r="M42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="5"/>
+      <c r="A43" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="G43" s="5"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="5"/>
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J43" s="5"/>
-      <c r="K43" s="3"/>
+      <c r="K43" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
+      <c r="M43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="5"/>
+      <c r="A44" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="G44" s="5"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="5"/>
+      <c r="H44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J44" s="5"/>
-      <c r="K44" s="3"/>
+      <c r="K44" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
+      <c r="M44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="5"/>
+      <c r="A45" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>60</v>
+      </c>
       <c r="G45" s="5"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="5"/>
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J45" s="5"/>
-      <c r="K45" s="3"/>
+      <c r="K45" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
+      <c r="M45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="5"/>
+      <c r="A46" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="G46" s="5"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="5"/>
+      <c r="H46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J46" s="5"/>
-      <c r="K46" s="3"/>
+      <c r="K46" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
+      <c r="M46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="5"/>
+      <c r="A47" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="G47" s="5"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="5"/>
+      <c r="H47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J47" s="5"/>
-      <c r="K47" s="3"/>
+      <c r="K47" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
+      <c r="M47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="5"/>
+      <c r="A48" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G48" s="5"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="5"/>
+      <c r="H48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="3"/>
+      <c r="K48" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
+      <c r="M48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="5"/>
+      <c r="A49" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="G49" s="5"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="5"/>
+      <c r="H49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J49" s="5"/>
-      <c r="K49" s="3"/>
+      <c r="K49" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
+      <c r="M49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="5"/>
+      <c r="A50" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="G50" s="5"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="5"/>
+      <c r="H50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J50" s="5"/>
-      <c r="K50" s="3"/>
+      <c r="K50" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
+      <c r="M50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="5"/>
+      <c r="A51" s="4" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="G51" s="5"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="5"/>
+      <c r="H51" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="J51" s="5"/>
-      <c r="K51" s="3"/>
+      <c r="K51" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
+      <c r="M51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>

--- a/Logs/Incoming Inspection Logs/MDL-004_Incoming_Inspection.xlsx
+++ b/Logs/Incoming Inspection Logs/MDL-004_Incoming_Inspection.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="75">
   <si>
     <t xml:space="preserve">Incoming Inspection Log</t>
   </si>
@@ -60,6 +60,9 @@
     <t xml:space="preserve">NCM Number</t>
   </si>
   <si>
+    <t xml:space="preserve">NCM Notes</t>
+  </si>
+  <si>
     <t xml:space="preserve">MSD</t>
   </si>
   <si>
@@ -220,6 +223,30 @@
   </si>
   <si>
     <t xml:space="preserve">FANDC5V4040mmPWMTACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P00001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JLCPCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1012202501-PCB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122925-0001 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB was specified at 2oz copper and was ordered at 1oz copper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1012202501-STENCIL-01-BOTTOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1012202501-STENCIL-01-TOP</t>
   </si>
 </sst>
 </file>
@@ -309,7 +336,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -326,12 +353,24 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -457,15 +496,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.32"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -482,8 +521,14 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -498,6 +543,12 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -536,1878 +587,2260 @@
       <c r="N3" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="O3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>46008</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>46008</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="5"/>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="6"/>
       <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="I4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="6"/>
       <c r="K4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="5"/>
+      <c r="I5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="6"/>
       <c r="K5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="5"/>
+      <c r="I6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="6"/>
       <c r="K6" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="5"/>
+      <c r="I7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="6"/>
       <c r="K7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="6"/>
+      <c r="H8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="5"/>
+      <c r="I8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="6"/>
       <c r="K8" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="5"/>
+      <c r="I9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="6"/>
       <c r="K9" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="5"/>
+      <c r="I10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="6"/>
       <c r="K10" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="5"/>
+      <c r="I11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="6"/>
       <c r="K11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="5"/>
+      <c r="I12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="6"/>
       <c r="K12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="6"/>
+      <c r="H13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="5"/>
+      <c r="I13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="6"/>
       <c r="K13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="5"/>
+      <c r="I14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="6"/>
       <c r="K14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="5"/>
+      <c r="I15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="6"/>
       <c r="K15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="6"/>
+      <c r="H16" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="5"/>
+      <c r="I16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="6"/>
       <c r="K16" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6"/>
+      <c r="H17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N16" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="5"/>
+      <c r="I17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="6"/>
       <c r="K17" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="5"/>
+      <c r="I18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="6"/>
       <c r="K18" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="6"/>
+      <c r="H19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="5"/>
+      <c r="I19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="6"/>
       <c r="K19" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="6"/>
+      <c r="H20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="5"/>
+      <c r="I20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="6"/>
       <c r="K20" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="5"/>
+      <c r="I21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="6"/>
       <c r="K21" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="5"/>
+      <c r="I22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="6"/>
       <c r="K22" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="5"/>
+      <c r="I23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="6"/>
       <c r="K23" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G24" s="6"/>
+      <c r="H24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="5"/>
+      <c r="I24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="6"/>
       <c r="K24" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="5"/>
+      <c r="I25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="6"/>
       <c r="K25" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="6"/>
+      <c r="H26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="5"/>
+      <c r="I26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="6"/>
       <c r="K26" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="5"/>
+      <c r="I27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="6"/>
       <c r="K27" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="6"/>
+      <c r="H28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="5"/>
+      <c r="I28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="6"/>
       <c r="K28" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="6"/>
+      <c r="H29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N28" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="5"/>
+      <c r="I29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="6"/>
       <c r="K29" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="5"/>
+      <c r="I30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="6"/>
       <c r="K30" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="6"/>
+      <c r="H31" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N30" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="5"/>
+      <c r="I31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="6"/>
       <c r="K31" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="6"/>
+      <c r="H32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N31" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="5"/>
+      <c r="I32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="6"/>
       <c r="K32" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" s="6"/>
+      <c r="H33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="5"/>
+      <c r="I33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="6"/>
       <c r="K33" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="6"/>
+      <c r="H34" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="5"/>
+      <c r="I34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="6"/>
       <c r="K34" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="6"/>
+      <c r="H35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N34" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="5"/>
+      <c r="I35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="6"/>
       <c r="K35" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="6"/>
+      <c r="H36" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="5"/>
+      <c r="I36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="6"/>
       <c r="K36" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="6"/>
+      <c r="H37" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N36" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="5"/>
+      <c r="I37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="6"/>
       <c r="K37" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="6"/>
+      <c r="H38" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N37" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G38" s="5"/>
-      <c r="H38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="5"/>
+      <c r="I38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="6"/>
       <c r="K38" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="6"/>
+      <c r="H39" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N38" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="5"/>
+      <c r="I39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="6"/>
       <c r="K39" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="6"/>
+      <c r="H40" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N39" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="5"/>
+      <c r="I40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="6"/>
       <c r="K40" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N40" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="5"/>
+      <c r="I41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="6"/>
       <c r="K41" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="5"/>
+      <c r="I42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="6"/>
       <c r="K42" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="6"/>
+      <c r="H43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="5"/>
+      <c r="I43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="6"/>
       <c r="K43" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="6"/>
+      <c r="H44" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="5"/>
+      <c r="I44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="6"/>
       <c r="K44" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="5"/>
+      <c r="I45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="6"/>
       <c r="K45" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="5"/>
+      <c r="I46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="6"/>
       <c r="K46" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G47" s="6"/>
+      <c r="H47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="5"/>
+      <c r="I47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="6"/>
       <c r="K47" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" s="6"/>
+      <c r="H48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="5"/>
+      <c r="I48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="6"/>
       <c r="K48" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+      <c r="R48" s="7"/>
+      <c r="S48" s="7"/>
+      <c r="T48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="5"/>
+      <c r="I49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="6"/>
       <c r="K49" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+      <c r="R49" s="7"/>
+      <c r="S49" s="7"/>
+      <c r="T49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="5"/>
+      <c r="I50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="6"/>
       <c r="K50" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+      <c r="R50" s="7"/>
+      <c r="S50" s="7"/>
+      <c r="T50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>46008</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G51" s="6"/>
+      <c r="H51" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N50" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>46009</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>46008</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="5"/>
+      <c r="I51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="6"/>
       <c r="K51" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
+      <c r="R51" s="7"/>
+      <c r="S51" s="7"/>
+      <c r="T51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>46020</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N51" s="3" t="s">
+      <c r="I52" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="3"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
+      <c r="M52" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="O52" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="P52" s="7"/>
+      <c r="Q52" s="7"/>
+      <c r="R52" s="7"/>
+      <c r="S52" s="7"/>
+      <c r="T52" s="7"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="3"/>
+      <c r="A53" s="5" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>46020</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="G53" s="6"/>
+      <c r="H53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="6"/>
+      <c r="K53" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
+      <c r="M53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O53" s="7"/>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="7"/>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="7"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="3"/>
+      <c r="A54" s="5" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>46020</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="6"/>
+      <c r="K54" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
+      <c r="M54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O54" s="7"/>
+      <c r="P54" s="7"/>
+      <c r="Q54" s="7"/>
+      <c r="R54" s="7"/>
+      <c r="S54" s="7"/>
+      <c r="T54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
@@ -2415,15 +2848,21 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
+      <c r="O55" s="7"/>
+      <c r="P55" s="7"/>
+      <c r="Q55" s="7"/>
+      <c r="R55" s="7"/>
+      <c r="S55" s="7"/>
+      <c r="T55" s="7"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
@@ -2431,15 +2870,21 @@
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
       <c r="H56" s="3"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
+      <c r="O56" s="7"/>
+      <c r="P56" s="7"/>
+      <c r="Q56" s="7"/>
+      <c r="R56" s="7"/>
+      <c r="S56" s="7"/>
+      <c r="T56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
@@ -2447,15 +2892,21 @@
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7"/>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
@@ -2463,15 +2914,21 @@
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
       <c r="H58" s="3"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
+      <c r="O58" s="7"/>
+      <c r="P58" s="7"/>
+      <c r="Q58" s="7"/>
+      <c r="R58" s="7"/>
+      <c r="S58" s="7"/>
+      <c r="T58" s="7"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
@@ -2479,15 +2936,21 @@
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
+      <c r="O59" s="7"/>
+      <c r="P59" s="7"/>
+      <c r="Q59" s="7"/>
+      <c r="R59" s="7"/>
+      <c r="S59" s="7"/>
+      <c r="T59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
@@ -2495,15 +2958,21 @@
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
       <c r="H60" s="3"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
@@ -2511,15 +2980,21 @@
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
+      <c r="O61" s="7"/>
+      <c r="P61" s="7"/>
+      <c r="Q61" s="7"/>
+      <c r="R61" s="7"/>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
@@ -2527,15 +3002,21 @@
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
       <c r="H62" s="3"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
+      <c r="O62" s="7"/>
+      <c r="P62" s="7"/>
+      <c r="Q62" s="7"/>
+      <c r="R62" s="7"/>
+      <c r="S62" s="7"/>
+      <c r="T62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
@@ -2543,15 +3024,21 @@
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
+      <c r="O63" s="7"/>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
+      <c r="R63" s="7"/>
+      <c r="S63" s="7"/>
+      <c r="T63" s="7"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
@@ -2559,15 +3046,21 @@
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
       <c r="H64" s="3"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
+      <c r="O64" s="7"/>
+      <c r="P64" s="7"/>
+      <c r="Q64" s="7"/>
+      <c r="R64" s="7"/>
+      <c r="S64" s="7"/>
+      <c r="T64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
@@ -2575,15 +3068,21 @@
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
       <c r="H65" s="3"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
+      <c r="O65" s="7"/>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
+      <c r="R65" s="7"/>
+      <c r="S65" s="7"/>
+      <c r="T65" s="7"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
@@ -2591,15 +3090,21 @@
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
       <c r="H66" s="3"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
+      <c r="O66" s="7"/>
+      <c r="P66" s="7"/>
+      <c r="Q66" s="7"/>
+      <c r="R66" s="7"/>
+      <c r="S66" s="7"/>
+      <c r="T66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
@@ -2607,15 +3112,21 @@
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
       <c r="H67" s="3"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7"/>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
@@ -2623,15 +3134,21 @@
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
       <c r="H68" s="3"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
+      <c r="O68" s="7"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
+      <c r="R68" s="7"/>
+      <c r="S68" s="7"/>
+      <c r="T68" s="7"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
@@ -2639,15 +3156,21 @@
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
+      <c r="O69" s="7"/>
+      <c r="P69" s="7"/>
+      <c r="Q69" s="7"/>
+      <c r="R69" s="7"/>
+      <c r="S69" s="7"/>
+      <c r="T69" s="7"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3"/>
@@ -2655,223 +3178,297 @@
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
+      <c r="O70" s="7"/>
+      <c r="P70" s="7"/>
+      <c r="Q70" s="7"/>
+      <c r="R70" s="7"/>
+      <c r="S70" s="7"/>
+      <c r="T70" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="205">
-    <mergeCell ref="A1:N2"/>
+  <mergeCells count="273">
+    <mergeCell ref="A1:T2"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
+    <mergeCell ref="O3:T3"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="K4:L4"/>
+    <mergeCell ref="O4:T4"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="K5:L5"/>
+    <mergeCell ref="O5:T5"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="K6:L6"/>
+    <mergeCell ref="O6:T6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="K7:L7"/>
+    <mergeCell ref="O7:T7"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="K8:L8"/>
+    <mergeCell ref="O8:T8"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="K9:L9"/>
+    <mergeCell ref="O9:T9"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="K10:L10"/>
+    <mergeCell ref="O10:T10"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="I11:J11"/>
     <mergeCell ref="K11:L11"/>
+    <mergeCell ref="O11:T11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="K12:L12"/>
+    <mergeCell ref="O12:T12"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="K13:L13"/>
+    <mergeCell ref="O13:T13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="K14:L14"/>
+    <mergeCell ref="O14:T14"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="K15:L15"/>
+    <mergeCell ref="O15:T15"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="K16:L16"/>
+    <mergeCell ref="O16:T16"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="I17:J17"/>
     <mergeCell ref="K17:L17"/>
+    <mergeCell ref="O17:T17"/>
     <mergeCell ref="F18:G18"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="K18:L18"/>
+    <mergeCell ref="O18:T18"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="I19:J19"/>
     <mergeCell ref="K19:L19"/>
+    <mergeCell ref="O19:T19"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="K20:L20"/>
+    <mergeCell ref="O20:T20"/>
     <mergeCell ref="F21:G21"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="K21:L21"/>
+    <mergeCell ref="O21:T21"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="K22:L22"/>
+    <mergeCell ref="O22:T22"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="I23:J23"/>
     <mergeCell ref="K23:L23"/>
+    <mergeCell ref="O23:T23"/>
     <mergeCell ref="F24:G24"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="K24:L24"/>
+    <mergeCell ref="O24:T24"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="I25:J25"/>
     <mergeCell ref="K25:L25"/>
+    <mergeCell ref="O25:T25"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="I26:J26"/>
     <mergeCell ref="K26:L26"/>
+    <mergeCell ref="O26:T26"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="I27:J27"/>
     <mergeCell ref="K27:L27"/>
+    <mergeCell ref="O27:T27"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="I28:J28"/>
     <mergeCell ref="K28:L28"/>
+    <mergeCell ref="O28:T28"/>
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="I29:J29"/>
     <mergeCell ref="K29:L29"/>
+    <mergeCell ref="O29:T29"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="K30:L30"/>
+    <mergeCell ref="O30:T30"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="K31:L31"/>
+    <mergeCell ref="O31:T31"/>
     <mergeCell ref="F32:G32"/>
     <mergeCell ref="I32:J32"/>
     <mergeCell ref="K32:L32"/>
+    <mergeCell ref="O32:T32"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="K33:L33"/>
+    <mergeCell ref="O33:T33"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="K34:L34"/>
+    <mergeCell ref="O34:T34"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="K35:L35"/>
+    <mergeCell ref="O35:T35"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="K36:L36"/>
+    <mergeCell ref="O36:T36"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="K37:L37"/>
+    <mergeCell ref="O37:T37"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="K38:L38"/>
+    <mergeCell ref="O38:T38"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="I39:J39"/>
     <mergeCell ref="K39:L39"/>
+    <mergeCell ref="O39:T39"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="K40:L40"/>
+    <mergeCell ref="O40:T40"/>
     <mergeCell ref="F41:G41"/>
     <mergeCell ref="I41:J41"/>
     <mergeCell ref="K41:L41"/>
+    <mergeCell ref="O41:T41"/>
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="K42:L42"/>
+    <mergeCell ref="O42:T42"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="K43:L43"/>
+    <mergeCell ref="O43:T43"/>
     <mergeCell ref="F44:G44"/>
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="K44:L44"/>
+    <mergeCell ref="O44:T44"/>
     <mergeCell ref="F45:G45"/>
     <mergeCell ref="I45:J45"/>
     <mergeCell ref="K45:L45"/>
+    <mergeCell ref="O45:T45"/>
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="K46:L46"/>
+    <mergeCell ref="O46:T46"/>
     <mergeCell ref="F47:G47"/>
     <mergeCell ref="I47:J47"/>
     <mergeCell ref="K47:L47"/>
+    <mergeCell ref="O47:T47"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="I48:J48"/>
     <mergeCell ref="K48:L48"/>
+    <mergeCell ref="O48:T48"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="K49:L49"/>
+    <mergeCell ref="O49:T49"/>
     <mergeCell ref="F50:G50"/>
     <mergeCell ref="I50:J50"/>
     <mergeCell ref="K50:L50"/>
+    <mergeCell ref="O50:T50"/>
     <mergeCell ref="F51:G51"/>
     <mergeCell ref="I51:J51"/>
     <mergeCell ref="K51:L51"/>
+    <mergeCell ref="O51:T51"/>
     <mergeCell ref="F52:G52"/>
     <mergeCell ref="I52:J52"/>
     <mergeCell ref="K52:L52"/>
+    <mergeCell ref="O52:T52"/>
     <mergeCell ref="F53:G53"/>
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="K53:L53"/>
+    <mergeCell ref="O53:T53"/>
     <mergeCell ref="F54:G54"/>
     <mergeCell ref="I54:J54"/>
     <mergeCell ref="K54:L54"/>
+    <mergeCell ref="O54:T54"/>
     <mergeCell ref="F55:G55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="K55:L55"/>
+    <mergeCell ref="O55:T55"/>
     <mergeCell ref="F56:G56"/>
     <mergeCell ref="I56:J56"/>
     <mergeCell ref="K56:L56"/>
+    <mergeCell ref="O56:T56"/>
     <mergeCell ref="F57:G57"/>
     <mergeCell ref="I57:J57"/>
     <mergeCell ref="K57:L57"/>
+    <mergeCell ref="O57:T57"/>
     <mergeCell ref="F58:G58"/>
     <mergeCell ref="I58:J58"/>
     <mergeCell ref="K58:L58"/>
+    <mergeCell ref="O58:T58"/>
     <mergeCell ref="F59:G59"/>
     <mergeCell ref="I59:J59"/>
     <mergeCell ref="K59:L59"/>
+    <mergeCell ref="O59:T59"/>
     <mergeCell ref="F60:G60"/>
     <mergeCell ref="I60:J60"/>
     <mergeCell ref="K60:L60"/>
+    <mergeCell ref="O60:T60"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="I61:J61"/>
     <mergeCell ref="K61:L61"/>
+    <mergeCell ref="O61:T61"/>
     <mergeCell ref="F62:G62"/>
     <mergeCell ref="I62:J62"/>
     <mergeCell ref="K62:L62"/>
+    <mergeCell ref="O62:T62"/>
     <mergeCell ref="F63:G63"/>
     <mergeCell ref="I63:J63"/>
     <mergeCell ref="K63:L63"/>
+    <mergeCell ref="O63:T63"/>
     <mergeCell ref="F64:G64"/>
     <mergeCell ref="I64:J64"/>
     <mergeCell ref="K64:L64"/>
+    <mergeCell ref="O64:T64"/>
     <mergeCell ref="F65:G65"/>
     <mergeCell ref="I65:J65"/>
     <mergeCell ref="K65:L65"/>
+    <mergeCell ref="O65:T65"/>
     <mergeCell ref="F66:G66"/>
     <mergeCell ref="I66:J66"/>
     <mergeCell ref="K66:L66"/>
+    <mergeCell ref="O66:T66"/>
     <mergeCell ref="F67:G67"/>
     <mergeCell ref="I67:J67"/>
     <mergeCell ref="K67:L67"/>
+    <mergeCell ref="O67:T67"/>
     <mergeCell ref="F68:G68"/>
     <mergeCell ref="I68:J68"/>
     <mergeCell ref="K68:L68"/>
+    <mergeCell ref="O68:T68"/>
     <mergeCell ref="F69:G69"/>
     <mergeCell ref="I69:J69"/>
     <mergeCell ref="K69:L69"/>
+    <mergeCell ref="O69:T69"/>
     <mergeCell ref="F70:G70"/>
     <mergeCell ref="I70:J70"/>
     <mergeCell ref="K70:L70"/>
+    <mergeCell ref="O70:T70"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -2973,11 +3570,11 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -2989,11 +3586,11 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -3005,11 +3602,11 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -3021,11 +3618,11 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -3037,11 +3634,11 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -3053,11 +3650,11 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -3069,11 +3666,11 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -3085,11 +3682,11 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -3101,11 +3698,11 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -3117,11 +3714,11 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -3133,11 +3730,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -3149,11 +3746,11 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -3165,11 +3762,11 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -3181,11 +3778,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -3197,11 +3794,11 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -3213,11 +3810,11 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -3229,11 +3826,11 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -3245,11 +3842,11 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -3261,11 +3858,11 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -3277,11 +3874,11 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -3293,11 +3890,11 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -3309,11 +3906,11 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -3325,11 +3922,11 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -3341,11 +3938,11 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -3357,11 +3954,11 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -3373,11 +3970,11 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -3389,11 +3986,11 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -3405,11 +4002,11 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -3421,11 +4018,11 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -3437,11 +4034,11 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -3453,11 +4050,11 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -3469,11 +4066,11 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -3485,11 +4082,11 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -3501,11 +4098,11 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -3517,11 +4114,11 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -3533,11 +4130,11 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -3549,11 +4146,11 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
@@ -3565,11 +4162,11 @@
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -3581,11 +4178,11 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="3"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -3597,11 +4194,11 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
@@ -3613,11 +4210,11 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -3629,11 +4226,11 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
@@ -3645,11 +4242,11 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
@@ -3661,11 +4258,11 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
@@ -3677,11 +4274,11 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="3"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
@@ -3693,11 +4290,11 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
@@ -3709,11 +4306,11 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="3"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
@@ -3725,11 +4322,11 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -3741,11 +4338,11 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
       <c r="H52" s="3"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
@@ -3757,11 +4354,11 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -3773,11 +4370,11 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -3789,11 +4386,11 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -3805,11 +4402,11 @@
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
       <c r="H56" s="3"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -3821,11 +4418,11 @@
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
@@ -3837,11 +4434,11 @@
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
       <c r="H58" s="3"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
@@ -3853,11 +4450,11 @@
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
@@ -3869,11 +4466,11 @@
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
       <c r="H60" s="3"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
@@ -3885,11 +4482,11 @@
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
@@ -3901,11 +4498,11 @@
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
       <c r="H62" s="3"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
@@ -3917,11 +4514,11 @@
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
@@ -3933,11 +4530,11 @@
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
       <c r="H64" s="3"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
@@ -3949,11 +4546,11 @@
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
       <c r="H65" s="3"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
@@ -3965,11 +4562,11 @@
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
       <c r="H66" s="3"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
@@ -3981,11 +4578,11 @@
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
       <c r="H67" s="3"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
@@ -3997,11 +4594,11 @@
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
       <c r="H68" s="3"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
@@ -4013,11 +4610,11 @@
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
@@ -4029,11 +4626,11 @@
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
@@ -4347,11 +4944,11 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="3"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -4363,11 +4960,11 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
@@ -4379,11 +4976,11 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -4395,11 +4992,11 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -4411,11 +5008,11 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -4427,11 +5024,11 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -4443,11 +5040,11 @@
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -4459,11 +5056,11 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -4475,11 +5072,11 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -4491,11 +5088,11 @@
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -4507,11 +5104,11 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -4523,11 +5120,11 @@
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -4539,11 +5136,11 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -4555,11 +5152,11 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -4571,11 +5168,11 @@
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -4587,11 +5184,11 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -4603,11 +5200,11 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -4619,11 +5216,11 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -4635,11 +5232,11 @@
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="3"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -4651,11 +5248,11 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="3"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -4667,11 +5264,11 @@
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -4683,11 +5280,11 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="3"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -4699,11 +5296,11 @@
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="3"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -4715,11 +5312,11 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="3"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -4731,11 +5328,11 @@
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="3"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -4747,11 +5344,11 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="3"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -4763,11 +5360,11 @@
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -4779,11 +5376,11 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -4795,11 +5392,11 @@
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -4811,11 +5408,11 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -4827,11 +5424,11 @@
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -4843,11 +5440,11 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="3"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -4859,11 +5456,11 @@
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="3"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -4875,11 +5472,11 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
       <c r="H37" s="3"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -4891,11 +5488,11 @@
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
       <c r="H38" s="3"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -4907,11 +5504,11 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
       <c r="H39" s="3"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -4923,11 +5520,11 @@
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
@@ -4939,11 +5536,11 @@
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
       <c r="H41" s="3"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
@@ -4955,11 +5552,11 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
       <c r="H42" s="3"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
@@ -4971,11 +5568,11 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
       <c r="H43" s="3"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
@@ -4987,11 +5584,11 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
       <c r="H44" s="3"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
@@ -5003,11 +5600,11 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
       <c r="H45" s="3"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
@@ -5019,11 +5616,11 @@
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
       <c r="H46" s="3"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
@@ -5035,11 +5632,11 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
       <c r="H47" s="3"/>
-      <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
@@ -5051,11 +5648,11 @@
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
       <c r="H48" s="3"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
@@ -5067,11 +5664,11 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
       <c r="H49" s="3"/>
-      <c r="I49" s="5"/>
-      <c r="J49" s="5"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
@@ -5083,11 +5680,11 @@
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
       <c r="H50" s="3"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
@@ -5099,11 +5696,11 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
       <c r="H51" s="3"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -5115,11 +5712,11 @@
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
       <c r="H52" s="3"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
@@ -5131,11 +5728,11 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
       <c r="H53" s="3"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
@@ -5147,11 +5744,11 @@
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
@@ -5163,11 +5760,11 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
       <c r="H55" s="3"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
@@ -5179,11 +5776,11 @@
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
       <c r="H56" s="3"/>
-      <c r="I56" s="5"/>
-      <c r="J56" s="5"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
@@ -5195,11 +5792,11 @@
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="5"/>
-      <c r="J57" s="5"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
@@ -5211,11 +5808,11 @@
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
       <c r="H58" s="3"/>
-      <c r="I58" s="5"/>
-      <c r="J58" s="5"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
@@ -5227,11 +5824,11 @@
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="5"/>
-      <c r="J59" s="5"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
@@ -5243,11 +5840,11 @@
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
       <c r="H60" s="3"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
@@ -5259,11 +5856,11 @@
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
       <c r="H61" s="3"/>
-      <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
@@ -5275,11 +5872,11 @@
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
       <c r="H62" s="3"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
@@ -5291,11 +5888,11 @@
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
       <c r="H63" s="3"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
@@ -5307,11 +5904,11 @@
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
       <c r="H64" s="3"/>
-      <c r="I64" s="5"/>
-      <c r="J64" s="5"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
@@ -5323,11 +5920,11 @@
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
       <c r="H65" s="3"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
@@ -5339,11 +5936,11 @@
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
       <c r="H66" s="3"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
@@ -5355,11 +5952,11 @@
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
       <c r="H67" s="3"/>
-      <c r="I67" s="5"/>
-      <c r="J67" s="5"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
@@ -5371,11 +5968,11 @@
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
       <c r="H68" s="3"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
@@ -5387,11 +5984,11 @@
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
       <c r="H69" s="3"/>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
@@ -5403,11 +6000,11 @@
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
       <c r="H70" s="3"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
